--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -466,7 +466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sabareesh</t>
+          <t>sabareesh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -477,11 +477,33 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>922525106265</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sabarivasan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SabarivasanP</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -502,8 +502,30 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>92255106261</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Roshan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>roshan2403</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshan2403/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -524,8 +524,30 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>922525106268</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sakthi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sakthisaro08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -546,8 +546,30 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>922525106369</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Vishnu priyan S</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>itz__priyan__</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -546,30 +546,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>922525106369</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Vishnu priyan S</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>itz__priyan__</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/itz__priyan__/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D6"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -461,93 +461,1039 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sabareesh</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sabarivasan</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>92255106261</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Roshan</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>922525106258</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RITHISH R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rithish_</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithish_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>922525106259</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ROHITH V</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>RohithrohiV</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>922525106260</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ROOBAGAPRIYA R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Roobagapriya</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>922525106261</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Roshan M</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>roshan2403</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshan2403/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>922525106262</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ROSHIKA V</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>roshikaveeramalai</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>922525106263</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RUBESH C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rubesh_7</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>922525106264</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SABAREESH K</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sabareesh_karikalan</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>922525106265</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SABARIVASAN P</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SabarivasanP</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>922525106266</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAHANA.V</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sahanavijayakumar_0033</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>922525106268</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>sakthi</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAKTHI S</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Sakthisaro08</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>922525106269</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sakthivel. M</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sakthivel23116</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>922525106271</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SANDHOSH KUMAR R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sandhosh_30_R</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>922525106272</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SANJAY D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>itsmesanjay007</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>922525106273</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SANJAY P</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sanjay00675</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjay00675/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>922525106275</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SANJAY U</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SanjayUdayan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>922525106278</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SANMATHI R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sanmathi06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanmathi06/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>922525106279</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SANTHIYA T</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>santhiya0202</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhiya0202/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>922525106280</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SANTHOSH D</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>santhosh7811</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh7811/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>922525106282</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SANTHOSH PRIYAN S</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SANTHOSH PRIYAN S</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>922525106283</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SANTHOSH S</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SanthoshSathya260</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>922525106284</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Santhosh S</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>santhosh2407</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh2407/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>922525106285</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANTHOSH V</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>santhosh8760</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/santhosh8760/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>922525106286</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SARAN K</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>saran32</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saran32/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>922525106287</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SARAVANAN K</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>saravanan .k</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saravanan .k/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>922525106288</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SARAVANAN K</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>saravanan__k__</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>922525106289</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SARAVANAN S</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saravanan_7525</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>922525106290</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SARIKA M P</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sarika_5408</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarika_5408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>922525106291</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SARVESWARAN R</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sarvesh312008</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>922525106292</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SASHMIKA.P</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sashmikaprabhu</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>922525106296</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SELVAKUMAR K</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Selvakumarsk-32</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>922525106297</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SELVAPRAGADEESH S</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Selvapragadeesh</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>922525106300</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Senthil.S</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jna76WrjNd</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>922525106302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SHAHANA S</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>shahana_pandiraj04</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>922525106303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SHANTHINI C</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ShanthiniChelladurai</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>922525106305</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SHARATH P</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sharath_1010</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharath_1010/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>922525106307</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SHIVANI B</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>shivani208</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shivani208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>922525106308</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SHREE HARINI L</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Shree_Harini478</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>922525106309</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SHREE CHARAN T</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>shreecharan22</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shreecharan22/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>922525106310</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SIVA MANIKANDAN K</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9043374912</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/9043374912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>922525106311</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SIVA PRAKASH M</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sivaprakash_0406</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>922525106312</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SIVADHARSHINI D</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dharshinideivsigamani</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>922525106313</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SIVAGNANAM M</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sivagnanam3344</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>922525106314</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SIVANESH D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sivanesh2007</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>922525106315</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SIVANESH G</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GSIVANESH</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -923,577 +923,533 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106282</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SANTHOSH PRIYAN S</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SANTHOSH PRIYAN S/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106287</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>saravanan .k</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan .k/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>Senthil.S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>922525106314</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SIVANESH D</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>sivanesh2007</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>922525106315</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SIVANESH G</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>GSIVANESH</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D48"/>
+  <autoFilter ref="A1:D46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1448,8 +1448,30 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>922525106270</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SANDHIYA T</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>zklXTc9UAp</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/zklXTc9UAp/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,13 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +455,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>LeetCode Link</t>
         </is>
       </c>
@@ -476,6 +482,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
@@ -498,6 +509,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
@@ -520,6 +536,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
@@ -542,6 +563,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
@@ -564,6 +590,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
@@ -586,6 +617,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
@@ -608,6 +644,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
@@ -630,6 +671,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
@@ -652,6 +698,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
@@ -674,6 +725,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
@@ -696,6 +752,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
@@ -718,6 +779,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
@@ -740,6 +806,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
@@ -762,6 +833,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
@@ -784,6 +860,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
@@ -806,6 +887,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
@@ -828,6 +914,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
@@ -850,6 +941,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
@@ -872,6 +968,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
@@ -894,6 +995,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
@@ -916,6 +1022,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
@@ -938,6 +1049,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
@@ -960,6 +1076,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
@@ -982,6 +1103,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
@@ -1004,6 +1130,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
@@ -1026,6 +1157,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
@@ -1048,6 +1184,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
@@ -1070,6 +1211,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
@@ -1092,6 +1238,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
@@ -1114,6 +1265,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
@@ -1136,6 +1292,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
@@ -1158,6 +1319,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
@@ -1180,6 +1346,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
@@ -1202,6 +1373,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
@@ -1224,6 +1400,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
@@ -1246,6 +1427,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
@@ -1268,6 +1454,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
@@ -1290,6 +1481,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
@@ -1312,6 +1508,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
@@ -1334,6 +1535,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
@@ -1356,6 +1562,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
@@ -1378,6 +1589,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
@@ -1400,6 +1616,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
@@ -1422,6 +1643,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
@@ -1444,6 +1670,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
@@ -1466,12 +1697,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/zklXTc9UAp/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D47"/>
+  <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1706,8 +1706,35 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>922525106267</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SAJISH R</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SAJISH7</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SAJISH7/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E47"/>
+  <autoFilter ref="A1:E48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1733,8 +1733,35 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>922525106274</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SANJAY S</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sanjay_Sakthivel-2</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E48"/>
+  <autoFilter ref="A1:E49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1760,8 +1760,35 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>922525106282</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SANTHOSH PRIYAN S</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>8925787430</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/8925787430/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:E50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1787,8 +1787,35 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>922525106287</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SARAVANAN K</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>X01u2FNNX4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/X01u2FNNX4/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E50"/>
+  <autoFilter ref="A1:E51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1814,8 +1814,35 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>922525106293</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SASWIN D</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>saswin_88</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/saswin_88/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E51"/>
+  <autoFilter ref="A1:E52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1841,8 +1841,35 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>922525106294</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SATHANA SRI S K</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Sathana-1267</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sathana-1267/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E52"/>
+  <autoFilter ref="A1:E53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1868,8 +1868,35 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>922525106295</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SATHYA PRAKASAM KANNAN</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SATHYAPRAKASAM__7</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E53"/>
+  <autoFilter ref="A1:E54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1895,8 +1895,35 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>922525106298</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SELVARAGHAVAN</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>selvax07</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/selvax07/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E54"/>
+  <autoFilter ref="A1:E55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1922,8 +1922,35 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>922525106299</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SENTHAMIZHSELVAN K</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>senthamizh08</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/senthamizh08/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E55"/>
+  <autoFilter ref="A1:E56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1949,8 +1949,35 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>922525106301</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SETHUPATHI G</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sethupathi_1228</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sethupathi_1228/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E56"/>
+  <autoFilter ref="A1:E57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1976,8 +1976,35 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>922525106304</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SANTOSH SHAI SIRIL R</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>shandoshsai</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/shandoshsai/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E57"/>
+  <autoFilter ref="A1:E58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2003,8 +2003,35 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>922525106306</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SHARUKESH T</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sharukesh2008</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sharukesh2008/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E58"/>
+  <autoFilter ref="A1:E59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2030,8 +2030,35 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>922525106276</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SANJYAN S</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sanjayan37</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjayan37/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E59"/>
+  <autoFilter ref="A1:E60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1331,17 +1331,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Senthil.S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SENTHIL S</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2057,8 +2057,62 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>922525106279</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ARUN KUMAR M</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>arunkumar1004</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arunkumar1004/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>922525106381</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LOHITH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOHITHTs</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITHTs/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E60"/>
+  <autoFilter ref="A1:E62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2111,8 +2111,35 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>922525106380</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>HARJIT VASAN</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Harjit_Vasan</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Harjit_Vasan/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E62"/>
+  <autoFilter ref="A1:E63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -629,17 +629,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Roshan M</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>Sakthivel. M</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SENTHIL S</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SENTHIL S</t>
+          <t>ROSHAN M</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
@@ -845,17 +845,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sanjayan37</t>
+          <t>sanjayan31</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjayan37/</t>
+          <t>https://leetcode.com/u/sanjayan31/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -2060,7 +2060,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106379</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2138,8 +2138,35 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>922525106277</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SANJEVI</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sanjevi007</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sanjevi007/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
@@ -845,17 +845,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
@@ -2165,8 +2165,35 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>922525106255</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>RITHIK I</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rithik2008</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Rithik2008/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E64"/>
+  <autoFilter ref="A1:E65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2192,8 +2192,35 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>922525106369</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>VISHNU PRIYAN S</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>itz__priyan__</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/itz__priyan__/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E65"/>
+  <autoFilter ref="A1:E66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sakthivel. M</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
@@ -926,17 +926,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>Santhosh S</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SENTHIL S</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SENTHIL S</t>
+          <t>ROSHAN M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ROSHAN M</t>
+          <t>SAKTHIVEL. M</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -1007,17 +1007,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Santhosh S</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SENTHIL S</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SENTHIL S</t>
+          <t>ROSHAN M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ROSHAN M</t>
+          <t>SAKTHIVEL. M</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SAKTHIVEL. M</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -2146,7 +2146,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SANJEVI</t>
+          <t>SANJEVI P</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">

--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,14 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,11 +454,6 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>LeetCode Link</t>
         </is>
       </c>
@@ -482,11 +476,6 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
@@ -509,11 +498,6 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
@@ -536,11 +520,6 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
@@ -563,11 +542,6 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
@@ -590,11 +564,6 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
@@ -617,11 +586,6 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
@@ -644,11 +608,6 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
@@ -671,11 +630,6 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
@@ -698,11 +652,6 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
@@ -725,11 +674,6 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
@@ -752,11 +696,6 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
@@ -779,11 +718,6 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
@@ -806,11 +740,6 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
@@ -833,11 +762,6 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
@@ -860,11 +784,6 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
@@ -887,11 +806,6 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
@@ -914,11 +828,6 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
@@ -941,11 +850,6 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
@@ -968,11 +872,6 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
@@ -995,11 +894,6 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
@@ -1022,11 +916,6 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
@@ -1049,11 +938,6 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
@@ -1076,11 +960,6 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
@@ -1103,11 +982,6 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
@@ -1130,11 +1004,6 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
@@ -1157,11 +1026,6 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
@@ -1184,11 +1048,6 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
@@ -1211,11 +1070,6 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
@@ -1238,11 +1092,6 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
@@ -1265,11 +1114,6 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
@@ -1292,11 +1136,6 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
@@ -1319,11 +1158,6 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
@@ -1346,11 +1180,6 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
@@ -1373,11 +1202,6 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
@@ -1400,11 +1224,6 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
@@ -1427,11 +1246,6 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
@@ -1454,11 +1268,6 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
@@ -1481,11 +1290,6 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
@@ -1508,11 +1312,6 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
@@ -1535,11 +1334,6 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
@@ -1562,11 +1356,6 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
@@ -1589,11 +1378,6 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
@@ -1616,11 +1400,6 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
@@ -1643,11 +1422,6 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
@@ -1670,11 +1444,6 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
@@ -1697,11 +1466,6 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/zklXTc9UAp/</t>
         </is>
       </c>
@@ -1724,11 +1488,6 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/SAJISH7/</t>
         </is>
       </c>
@@ -1751,11 +1510,6 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
         </is>
       </c>
@@ -1778,11 +1532,6 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
@@ -1805,11 +1554,6 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
@@ -1832,11 +1576,6 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
@@ -1859,11 +1598,6 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Sathana-1267/</t>
         </is>
       </c>
@@ -1886,11 +1620,6 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
         </is>
       </c>
@@ -1913,11 +1642,6 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/selvax07/</t>
         </is>
       </c>
@@ -1940,11 +1664,6 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/senthamizh08/</t>
         </is>
       </c>
@@ -1967,11 +1686,6 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Sethupathi_1228/</t>
         </is>
       </c>
@@ -1994,11 +1708,6 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/shandoshsai/</t>
         </is>
       </c>
@@ -2021,11 +1730,6 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sharukesh2008/</t>
         </is>
       </c>
@@ -2048,11 +1752,6 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sanjayan31/</t>
         </is>
       </c>
@@ -2075,11 +1774,6 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/arunkumar1004/</t>
         </is>
       </c>
@@ -2102,11 +1796,6 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/LOHITHTs/</t>
         </is>
       </c>
@@ -2129,11 +1818,6 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Harjit_Vasan/</t>
         </is>
       </c>
@@ -2156,11 +1840,6 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/sanjevi007/</t>
         </is>
       </c>
@@ -2183,11 +1862,6 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ECE E</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/Rithik2008/</t>
         </is>
       </c>
@@ -2210,17 +1884,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ECE F</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
           <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E66"/>
+  <autoFilter ref="A1:D66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$D$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$66</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,13 +427,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +455,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>LeetCode Link</t>
         </is>
       </c>
@@ -476,6 +482,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
@@ -498,6 +509,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
@@ -520,6 +536,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
@@ -542,6 +563,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
@@ -564,6 +590,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
@@ -586,6 +617,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
@@ -608,6 +644,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
@@ -630,6 +671,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
@@ -652,6 +698,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
@@ -674,6 +725,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
@@ -696,6 +752,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
@@ -718,6 +779,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
@@ -740,6 +806,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
@@ -762,6 +833,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
@@ -784,6 +860,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
@@ -806,6 +887,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
@@ -828,6 +914,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
@@ -850,6 +941,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
@@ -872,6 +968,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
@@ -894,6 +995,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
@@ -916,6 +1022,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
@@ -938,6 +1049,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
@@ -960,6 +1076,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
@@ -982,6 +1103,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
@@ -1004,6 +1130,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
@@ -1026,6 +1157,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
@@ -1048,6 +1184,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
@@ -1070,6 +1211,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
@@ -1092,6 +1238,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
@@ -1114,6 +1265,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
@@ -1136,6 +1292,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
@@ -1158,6 +1319,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
@@ -1180,6 +1346,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
@@ -1202,6 +1373,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
@@ -1224,6 +1400,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
@@ -1246,6 +1427,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
@@ -1268,6 +1454,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
@@ -1290,6 +1481,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
@@ -1312,6 +1508,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
@@ -1334,6 +1535,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
@@ -1356,6 +1562,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
@@ -1378,6 +1589,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
@@ -1400,6 +1616,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
@@ -1422,6 +1643,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
@@ -1444,6 +1670,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
@@ -1466,6 +1697,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/zklXTc9UAp/</t>
         </is>
       </c>
@@ -1488,6 +1724,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SAJISH7/</t>
         </is>
       </c>
@@ -1510,6 +1751,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sanjay_Sakthivel-2/</t>
         </is>
       </c>
@@ -1532,6 +1778,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/8925787430/</t>
         </is>
       </c>
@@ -1554,6 +1805,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/X01u2FNNX4/</t>
         </is>
       </c>
@@ -1576,6 +1832,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/saswin_88/</t>
         </is>
       </c>
@@ -1598,6 +1859,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sathana-1267/</t>
         </is>
       </c>
@@ -1620,6 +1886,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/SATHYAPRAKASAM__7/</t>
         </is>
       </c>
@@ -1642,6 +1913,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/selvax07/</t>
         </is>
       </c>
@@ -1664,6 +1940,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/senthamizh08/</t>
         </is>
       </c>
@@ -1686,6 +1967,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Sethupathi_1228/</t>
         </is>
       </c>
@@ -1708,6 +1994,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/shandoshsai/</t>
         </is>
       </c>
@@ -1730,6 +2021,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sharukesh2008/</t>
         </is>
       </c>
@@ -1752,6 +2048,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanjayan31/</t>
         </is>
       </c>
@@ -1774,6 +2075,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/arunkumar1004/</t>
         </is>
       </c>
@@ -1796,6 +2102,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/LOHITHTs/</t>
         </is>
       </c>
@@ -1818,6 +2129,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Harjit_Vasan/</t>
         </is>
       </c>
@@ -1840,6 +2156,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/sanjevi007/</t>
         </is>
       </c>
@@ -1862,6 +2183,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>ECE E</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/Rithik2008/</t>
         </is>
       </c>
@@ -1884,12 +2210,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>https://leetcode.com/u/itz__priyan__/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D66"/>
+  <autoFilter ref="A1:E66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
@@ -2219,8 +2219,737 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>922525106236</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PRITHIV S</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prithiv25</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Prithiv25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>922525106195</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MAYUKA M</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Mayuka_25</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mayuka_25/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>922525106214</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NITHISH C T</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Nithish12322</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithish12322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>922525106225</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PIRAVEEN M</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Piraveen_M</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Piraveen_M/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>922525106211</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NAVEETHA N</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Naveetha_</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Naveetha_/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>922525106199</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MONISH S</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MonishS77</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/MonishS77/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>922525106232</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PRAVEEN G</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>praveen_gobi</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/praveen_gobi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>922525106349</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>THAMEEM FARSHITHA A</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Thameem_786</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Thameem_786/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>922525106342</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SUSIDHARAN M</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>susidharan 147</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/susidharan 147/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>922525106329</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SRINITHE T</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>srinithe_1401</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>922525106032</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ARVINSHANKARA V</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ok</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Ok/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>922525106027</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ARULESH K</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>arul2008</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/arul2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>922525106049</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BUVNESH N</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Buvnesh_2008</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Buvnesh_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>922525106047</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BOSVIYA P</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BosviyaBSV</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>922525106373</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>YASHNI S</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yashnisubramaniyan</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>922525106059</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DEJASRI M</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>dejasri</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dejasri/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>922525106014</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AKASH R</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AkashRajaram</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>922525106009</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AISHWARYA G</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Codewithaish</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Codewithaish/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>922525106125</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JAI GANESH I</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Jai_Ganesh_I</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>922525106186</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MAHIBALAN A</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lakshmiprabha1984-prog</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>922525106160</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KOHUL V</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Kohul_v</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Kohul_v/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>922525106144</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KARMUKILAN J</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>karmukilan567</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/karmukilan567/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>922525106180</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MADHUDHARA P</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>madhudhara</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/madhudhara/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>922525106189</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MANISHA D</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>manishaa_20</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/manishaa_20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>922525106183</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MAHALAKSHMI B</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>mahalakshmi182025</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>922525106184</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MAHALAKSHMI M</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Maha ece</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Maha ece/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>922525106156</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KEERTHANA S</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hwfrd8kp5Y</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E66"/>
+  <autoFilter ref="A1:E93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2222,734 +2222,1247 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prithiv25</t>
+          <t>Jai_Ganesh_I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Prithiv25/</t>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>MAHIBALAN A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mayuka_25</t>
+          <t>lakshmiprabha1984-prog</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_25/</t>
+          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nithish12322</t>
+          <t>Kohul_v</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish12322/</t>
+          <t>https://leetcode.com/u/Kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Piraveen_M</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen_M/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NAVEETHA N</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Naveetha_</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Naveetha_/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>MANISHA D</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MonishS77</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishS77/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>praveen_gobi</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_gobi/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106184</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>MAHALAKSHMI M</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Maha ece</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Maha ece/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>susidharan 147</t>
+          <t>Hwfrd8kp5Y</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/susidharan 147/</t>
+          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Prithiv25</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Prithiv25/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ARVINSHANKARA V</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Mayuka_25</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ok/</t>
+          <t>https://leetcode.com/u/Mayuka_25/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ARULESH K</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>Nithish12322</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/Nithish12322/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Buvnesh_2008</t>
+          <t>Piraveen_M</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Buvnesh_2008/</t>
+          <t>https://leetcode.com/u/Piraveen_M/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>NAVEETHA N</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>Naveetha_</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/Naveetha_/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106199</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>MONISH S</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>yashnisubramaniyan</t>
+          <t>MonishS77</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/MonishS77/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>praveen_gobi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/praveen_gobi/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AKASH R</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>susidharan 147</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/susidharan 147/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Codewithaish</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Codewithaish/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jai_Ganesh_I</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106032</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MAHIBALAN A</t>
+          <t>ARVINSHANKARA V</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>lakshmiprabha1984-prog</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
+          <t>https://leetcode.com/u/Ok/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>ARULESH K</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kohul_v</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kohul_v/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Buvnesh_2008</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Buvnesh_2008/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MANISHA D</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106184</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI M</t>
+          <t>AKASH R</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Maha ece</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Maha ece/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106009</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>AISHWARYA G</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hwfrd8kp5Y</t>
+          <t>Codewithaish</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Codewithaish/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>922525106142</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KANITHRA R</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>kanithraakila</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
           <t>ECE C</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kanithraakila/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>922525106102</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GOWSICK S</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>922525000000</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/922525000000/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>922525106177</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MADELIN JENITA M</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jenita0206</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/jenita0206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>922525106043</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BHARGAVI K</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>bhargavi_332008</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/bhargavi_332008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>922525106339</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SUJITH RAJA B</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>sujith45</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sujith45/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>922525106054</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DAKSHINYA R</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Dakshinya555</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dakshinya555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>922525106175</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LOHITH RAJ S</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LOHITH 012008</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/LOHITH 012008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>922525106319</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SIVATHARUN C</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>sivatharun22</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/sivatharun22/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>922525106359</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VASANTHKUMAR R</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>VasanthKumar008</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/VasanthKumar008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>922525106318</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SIVASUBRAMANI A</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AK_Siva</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AK_Siva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>922525106127</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JANANI A</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>janani_asohkan</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/janani_asohkan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>922525106045</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BOOBASE R</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Boobase</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Boobase/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>922525106321</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SREE DHARANI C</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SREEDHARANI_14</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>922525106152</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KAVIPRIYA R</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>KAVI_RAVI</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>922525106332</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SUBARNA V</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Subarna1017</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Subarna1017/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>922525106208</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NANDHINI D</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>nandhini _208</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nandhini _208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>922525106205</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MYTHILI M</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Mythili_2208</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Mythili_2208/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>922525106079</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DHINAKAR A</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>dhina</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/dhina/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>922525106341</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SURYA PRABHU S</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SURYA_FOUNDER</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/SURYA_FOUNDER/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E93"/>
+  <autoFilter ref="A1:E112"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Students.xlsx
+++ b/Students.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Students'!$A$1:$E$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -467,17 +467,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>922525106253</t>
+          <t>922525106310</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RITHANYA KN</t>
+          <t>SIVA MANIKANDAN K</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rithanya12-3</t>
+          <t>9043374912</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithanya12-3/</t>
+          <t>https://leetcode.com/u/9043374912/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>922525106256</t>
+          <t>922525106290</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RITHIK P</t>
+          <t>SARIKA M P</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rithik_78</t>
+          <t>sarika_5408</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithik_78/</t>
+          <t>https://leetcode.com/u/sarika_5408/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>922525106257</t>
+          <t>922525106291</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RITHIKA B</t>
+          <t>SARVESWARAN R</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rithika_Balakrishnan</t>
+          <t>sarvesh312008</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
+          <t>https://leetcode.com/u/sarvesh312008/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>922525106258</t>
+          <t>922525106292</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RITHISH R</t>
+          <t>SASHMIKA.P</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rithish_</t>
+          <t>sashmikaprabhu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rithish_/</t>
+          <t>https://leetcode.com/u/sashmikaprabhu/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>922525106259</t>
+          <t>922525106296</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ROHITH V</t>
+          <t>SELVAKUMAR K</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RohithrohiV</t>
+          <t>Selvakumarsk-32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/RohithrohiV/</t>
+          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>922525106260</t>
+          <t>922525106297</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ROOBAGAPRIYA R</t>
+          <t>SELVAPRAGADEESH S</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Roobagapriya</t>
+          <t>Selvapragadeesh</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Roobagapriya/</t>
+          <t>https://leetcode.com/u/Selvapragadeesh/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>922525106262</t>
+          <t>922525106302</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ROSHIKA V</t>
+          <t>SHAHANA S</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>roshikaveeramalai</t>
+          <t>shahana_pandiraj04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -649,24 +649,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshikaveeramalai/</t>
+          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>922525106263</t>
+          <t>922525106303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RUBESH C</t>
+          <t>SHANTHINI C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rubesh_7</t>
+          <t>ShanthiniChelladurai</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Rubesh_7/</t>
+          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>922525106264</t>
+          <t>922525106305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SABAREESH K</t>
+          <t>SHARATH P</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sabareesh_karikalan</t>
+          <t>sharath_1010</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
+          <t>https://leetcode.com/u/sharath_1010/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>922525106265</t>
+          <t>922525106307</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SABARIVASAN P</t>
+          <t>SHIVANI B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SabarivasanP</t>
+          <t>shivani208</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SabarivasanP/</t>
+          <t>https://leetcode.com/u/shivani208/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>922525106266</t>
+          <t>922525106308</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAHANA.V</t>
+          <t>SHREE HARINI L</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sahanavijayakumar_0033</t>
+          <t>Shree_Harini478</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
+          <t>https://leetcode.com/u/Shree_Harini478/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>922525106268</t>
+          <t>922525106300</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAKTHI S</t>
+          <t>SENTHIL S</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sakthisaro08</t>
+          <t>Jna76WrjNd</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Sakthisaro08/</t>
+          <t>https://leetcode.com/u/Jna76WrjNd/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>922525106271</t>
+          <t>922525106261</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDHOSH KUMAR R</t>
+          <t>ROSHAN M</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sandhosh_30_R</t>
+          <t>roshan2403</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sandhosh_30_R/</t>
+          <t>https://leetcode.com/u/roshan2403/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>922525106272</t>
+          <t>922525106269</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANJAY D</t>
+          <t>SAKTHIVEL. M</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>itsmesanjay007</t>
+          <t>sakthivel23116</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/itsmesanjay007/</t>
+          <t>https://leetcode.com/u/sakthivel23116/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>922525106273</t>
+          <t>922525106284</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANJAY P</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sanjay00675</t>
+          <t>santhosh2407</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanjay00675/</t>
+          <t>https://leetcode.com/u/santhosh2407/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>922525106275</t>
+          <t>922525106315</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANJAY U</t>
+          <t>SIVANESH G</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SanjayUdayan</t>
+          <t>GSIVANESH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanjayUdayan/</t>
+          <t>https://leetcode.com/u/GSIVANESH/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>922525106278</t>
+          <t>922525106314</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANMATHI R</t>
+          <t>SIVANESH D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sanmathi06</t>
+          <t>sivanesh2007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sanmathi06/</t>
+          <t>https://leetcode.com/u/sivanesh2007/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>922525106279</t>
+          <t>922525106313</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANTHIYA T</t>
+          <t>SIVAGNANAM M</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>santhiya0202</t>
+          <t>sivagnanam3344</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhiya0202/</t>
+          <t>https://leetcode.com/u/sivagnanam3344/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922525106280</t>
+          <t>922525106312</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANTHOSH D</t>
+          <t>SIVADHARSHINI D</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>santhosh7811</t>
+          <t>dharshinideivsigamani</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh7811/</t>
+          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>922525106283</t>
+          <t>922525106311</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SIVA PRAKASH M</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SanthoshSathya260</t>
+          <t>sivaprakash_0406</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SanthoshSathya260/</t>
+          <t>https://leetcode.com/u/sivaprakash_0406/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>922525106285</t>
+          <t>922525106309</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANTHOSH V</t>
+          <t>SHREE CHARAN T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>santhosh8760</t>
+          <t>shreecharan22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh8760/</t>
+          <t>https://leetcode.com/u/shreecharan22/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>922525106286</t>
+          <t>922525106253</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SARAN K</t>
+          <t>RITHANYA KN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>saran32</t>
+          <t>Rithanya12-3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saran32/</t>
+          <t>https://leetcode.com/u/Rithanya12-3/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>922525106288</t>
+          <t>922525106256</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SARAVANAN K</t>
+          <t>RITHIK P</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>saravanan__k__</t>
+          <t>Rithik_78</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/saravanan__k__/</t>
+          <t>https://leetcode.com/u/Rithik_78/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>922525106289</t>
+          <t>922525106257</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SARAVANAN S</t>
+          <t>RITHIKA B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saravanan_7525</t>
+          <t>Rithika_Balakrishnan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Saravanan_7525/</t>
+          <t>https://leetcode.com/u/Rithika_Balakrishnan/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>922525106290</t>
+          <t>922525106258</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SARIKA M P</t>
+          <t>RITHISH R</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sarika_5408</t>
+          <t>Rithish_</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarika_5408/</t>
+          <t>https://leetcode.com/u/Rithish_/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>922525106291</t>
+          <t>922525106259</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SARVESWARAN R</t>
+          <t>ROHITH V</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sarvesh312008</t>
+          <t>RohithrohiV</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sarvesh312008/</t>
+          <t>https://leetcode.com/u/RohithrohiV/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>922525106292</t>
+          <t>922525106260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SASHMIKA.P</t>
+          <t>ROOBAGAPRIYA R</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sashmikaprabhu</t>
+          <t>Roobagapriya</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sashmikaprabhu/</t>
+          <t>https://leetcode.com/u/Roobagapriya/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>922525106296</t>
+          <t>922525106262</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SELVAKUMAR K</t>
+          <t>ROSHIKA V</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Selvakumarsk-32</t>
+          <t>roshikaveeramalai</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvakumarsk-32/</t>
+          <t>https://leetcode.com/u/roshikaveeramalai/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>922525106297</t>
+          <t>922525106263</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SELVAPRAGADEESH S</t>
+          <t>RUBESH C</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Selvapragadeesh</t>
+          <t>Rubesh_7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Selvapragadeesh/</t>
+          <t>https://leetcode.com/u/Rubesh_7/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>922525106302</t>
+          <t>922525106264</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SHAHANA S</t>
+          <t>SABAREESH K</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>shahana_pandiraj04</t>
+          <t>sabareesh_karikalan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shahana_pandiraj04/</t>
+          <t>https://leetcode.com/u/sabareesh_karikalan/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>922525106303</t>
+          <t>922525106265</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SHANTHINI C</t>
+          <t>SABARIVASAN P</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ShanthiniChelladurai</t>
+          <t>SabarivasanP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/ShanthiniChelladurai/</t>
+          <t>https://leetcode.com/u/SabarivasanP/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>922525106305</t>
+          <t>922525106266</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SHARATH P</t>
+          <t>SAHANA.V</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sharath_1010</t>
+          <t>Sahanavijayakumar_0033</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sharath_1010/</t>
+          <t>https://leetcode.com/u/Sahanavijayakumar_0033/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>922525106307</t>
+          <t>922525106268</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHIVANI B</t>
+          <t>SAKTHI S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shivani208</t>
+          <t>Sakthisaro08</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shivani208/</t>
+          <t>https://leetcode.com/u/Sakthisaro08/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>922525106308</t>
+          <t>922525106271</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHREE HARINI L</t>
+          <t>SANDHOSH KUMAR R</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shree_Harini478</t>
+          <t>sandhosh_30_R</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Shree_Harini478/</t>
+          <t>https://leetcode.com/u/sandhosh_30_R/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>922525106300</t>
+          <t>922525106272</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SENTHIL S</t>
+          <t>SANJAY D</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jna76WrjNd</t>
+          <t>itsmesanjay007</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jna76WrjNd/</t>
+          <t>https://leetcode.com/u/itsmesanjay007/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>922525106261</t>
+          <t>922525106273</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROSHAN M</t>
+          <t>SANJAY P</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>roshan2403</t>
+          <t>sanjay00675</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/roshan2403/</t>
+          <t>https://leetcode.com/u/sanjay00675/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>922525106269</t>
+          <t>922525106275</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SAKTHIVEL. M</t>
+          <t>SANJAY U</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>sakthivel23116</t>
+          <t>SanjayUdayan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sakthivel23116/</t>
+          <t>https://leetcode.com/u/SanjayUdayan/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>922525106284</t>
+          <t>922525106278</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SANTHOSH S</t>
+          <t>SANMATHI R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>santhosh2407</t>
+          <t>sanmathi06</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/santhosh2407/</t>
+          <t>https://leetcode.com/u/sanmathi06/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>922525106309</t>
+          <t>922525106279</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SHREE CHARAN T</t>
+          <t>SANTHIYA T</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shreecharan22</t>
+          <t>santhiya0202</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/shreecharan22/</t>
+          <t>https://leetcode.com/u/santhiya0202/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>922525106310</t>
+          <t>922525106280</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SIVA MANIKANDAN K</t>
+          <t>SANTHOSH D</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>9043374912</t>
+          <t>santhosh7811</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/9043374912/</t>
+          <t>https://leetcode.com/u/santhosh7811/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>922525106311</t>
+          <t>922525106283</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SIVA PRAKASH M</t>
+          <t>SANTHOSH S</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sivaprakash_0406</t>
+          <t>SanthoshSathya260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivaprakash_0406/</t>
+          <t>https://leetcode.com/u/SanthoshSathya260/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>922525106312</t>
+          <t>922525106285</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SIVADHARSHINI D</t>
+          <t>SANTHOSH V</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dharshinideivsigamani</t>
+          <t>santhosh8760</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dharshinideivsigamani/</t>
+          <t>https://leetcode.com/u/santhosh8760/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>922525106313</t>
+          <t>922525106286</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SIVAGNANAM M</t>
+          <t>SARAN K</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sivagnanam3344</t>
+          <t>saran32</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivagnanam3344/</t>
+          <t>https://leetcode.com/u/saran32/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>922525106314</t>
+          <t>922525106288</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SIVANESH D</t>
+          <t>SARAVANAN K</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sivanesh2007</t>
+          <t>saravanan__k__</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/sivanesh2007/</t>
+          <t>https://leetcode.com/u/saravanan__k__/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>922525106315</t>
+          <t>922525106289</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SIVANESH G</t>
+          <t>SARAVANAN S</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GSIVANESH</t>
+          <t>Saravanan_7525</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/GSIVANESH/</t>
+          <t>https://leetcode.com/u/Saravanan_7525/</t>
         </is>
       </c>
     </row>
@@ -2222,729 +2222,729 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>922525106125</t>
+          <t>922525106009</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JAI GANESH I</t>
+          <t>AISHWARYA G</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jai_Ganesh_I</t>
+          <t>Codewithaish</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
+          <t>https://leetcode.com/u/Codewithaish/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>922525106186</t>
+          <t>922525106032</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MAHIBALAN A</t>
+          <t>ARVINSHANKARA V</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>lakshmiprabha1984-prog</t>
+          <t>Ok</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
+          <t>https://leetcode.com/u/Ok/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>922525106160</t>
+          <t>922525106027</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KOHUL V</t>
+          <t>ARULESH K</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kohul_v</t>
+          <t>arul2008</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Kohul_v/</t>
+          <t>https://leetcode.com/u/arul2008/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>922525106144</t>
+          <t>922525106049</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KARMUKILAN J</t>
+          <t>BUVNESH N</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>karmukilan567</t>
+          <t>Buvnesh_2008</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/karmukilan567/</t>
+          <t>https://leetcode.com/u/Buvnesh_2008/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>922525106180</t>
+          <t>922525106047</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MADHUDHARA P</t>
+          <t>BOSVIYA P</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>madhudhara</t>
+          <t>BosviyaBSV</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/madhudhara/</t>
+          <t>https://leetcode.com/u/BosviyaBSV/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>922525106189</t>
+          <t>922525106373</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MANISHA D</t>
+          <t>YASHNI S</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>manishaa_20</t>
+          <t>yashnisubramaniyan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/manishaa_20/</t>
+          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>922525106183</t>
+          <t>922525106059</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI B</t>
+          <t>DEJASRI M</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mahalakshmi182025</t>
+          <t>dejasri</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/mahalakshmi182025/</t>
+          <t>https://leetcode.com/u/dejasri/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>922525106184</t>
+          <t>922525106014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI M</t>
+          <t>AKASH R</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Maha ece</t>
+          <t>AkashRajaram</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE A</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Maha ece/</t>
+          <t>https://leetcode.com/u/AkashRajaram/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>922525106156</t>
+          <t>922525106125</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KEERTHANA S</t>
+          <t>JAI GANESH I</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hwfrd8kp5Y</t>
+          <t>Jai_Ganesh_I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
+          <t>https://leetcode.com/u/Jai_Ganesh_I/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>922525106236</t>
+          <t>922525106186</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PRITHIV S</t>
+          <t>MAHIBALAN A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prithiv25</t>
+          <t>lakshmiprabha1984-prog</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Prithiv25/</t>
+          <t>https://leetcode.com/u/lakshmiprabha1984-prog/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>922525106195</t>
+          <t>922525106160</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MAYUKA M</t>
+          <t>KOHUL V</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mayuka_25</t>
+          <t>Kohul_v</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mayuka_25/</t>
+          <t>https://leetcode.com/u/Kohul_v/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>922525106214</t>
+          <t>922525106144</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NITHISH C T</t>
+          <t>KARMUKILAN J</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nithish12322</t>
+          <t>karmukilan567</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Nithish12322/</t>
+          <t>https://leetcode.com/u/karmukilan567/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>922525106225</t>
+          <t>922525106180</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PIRAVEEN M</t>
+          <t>MADHUDHARA P</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piraveen_M</t>
+          <t>madhudhara</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Piraveen_M/</t>
+          <t>https://leetcode.com/u/madhudhara/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>922525106211</t>
+          <t>922525106189</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NAVEETHA N</t>
+          <t>MANISHA D</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Naveetha_</t>
+          <t>manishaa_20</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Naveetha_/</t>
+          <t>https://leetcode.com/u/manishaa_20/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>922525106199</t>
+          <t>922525106183</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MONISH S</t>
+          <t>MAHALAKSHMI B</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MonishS77</t>
+          <t>mahalakshmi182025</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/MonishS77/</t>
+          <t>https://leetcode.com/u/mahalakshmi182025/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>922525106232</t>
+          <t>922525106184</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PRAVEEN G</t>
+          <t>MAHALAKSHMI M</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>praveen_gobi</t>
+          <t>Maha ece</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/praveen_gobi/</t>
+          <t>https://leetcode.com/u/Maha ece/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>922525106342</t>
+          <t>922525106156</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SUSIDHARAN M</t>
+          <t>KEERTHANA S</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>susidharan 147</t>
+          <t>Hwfrd8kp5Y</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/susidharan 147/</t>
+          <t>https://leetcode.com/u/Hwfrd8kp5Y/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>922525106329</t>
+          <t>922525106236</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRINITHE T</t>
+          <t>PRITHIV S</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>srinithe_1401</t>
+          <t>Prithiv25</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/srinithe_1401/</t>
+          <t>https://leetcode.com/u/Prithiv25/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>922525106349</t>
+          <t>922525106195</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>THAMEEM FARSHITHA A</t>
+          <t>MAYUKA M</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Thameem_786</t>
+          <t>Mayuka_25</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Thameem_786/</t>
+          <t>https://leetcode.com/u/Mayuka_25/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>922525106032</t>
+          <t>922525106214</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ARVINSHANKARA V</t>
+          <t>NITHISH C T</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ok</t>
+          <t>Nithish12322</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Ok/</t>
+          <t>https://leetcode.com/u/Nithish12322/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>922525106027</t>
+          <t>922525106225</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ARULESH K</t>
+          <t>PIRAVEEN M</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>arul2008</t>
+          <t>Piraveen_M</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/arul2008/</t>
+          <t>https://leetcode.com/u/Piraveen_M/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>922525106049</t>
+          <t>922525106211</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BUVNESH N</t>
+          <t>NAVEETHA N</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Buvnesh_2008</t>
+          <t>Naveetha_</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Buvnesh_2008/</t>
+          <t>https://leetcode.com/u/Naveetha_/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>922525106047</t>
+          <t>922525106199</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BOSVIYA P</t>
+          <t>MONISH S</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BosviyaBSV</t>
+          <t>MonishS77</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/BosviyaBSV/</t>
+          <t>https://leetcode.com/u/MonishS77/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>922525106373</t>
+          <t>922525106232</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YASHNI S</t>
+          <t>PRAVEEN G</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>yashnisubramaniyan</t>
+          <t>praveen_gobi</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/yashnisubramaniyan/</t>
+          <t>https://leetcode.com/u/praveen_gobi/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>922525106059</t>
+          <t>922525106349</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DEJASRI M</t>
+          <t>THAMEEM FARSHITHA A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>dejasri</t>
+          <t>Thameem_786</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dejasri/</t>
+          <t>https://leetcode.com/u/Thameem_786/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>922525106014</t>
+          <t>922525106342</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AKASH R</t>
+          <t>SUSIDHARAN M</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AkashRajaram</t>
+          <t>susidharan 147</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/AkashRajaram/</t>
+          <t>https://leetcode.com/u/susidharan 147/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>922525106009</t>
+          <t>922525106329</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AISHWARYA G</t>
+          <t>SRINITHE T</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Codewithaish</t>
+          <t>srinithe_1401</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ECE A</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Codewithaish/</t>
+          <t>https://leetcode.com/u/srinithe_1401/</t>
         </is>
       </c>
     </row>
@@ -3275,98 +3275,98 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>922525106321</t>
+          <t>922525106152</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SREE DHARANI C</t>
+          <t>KAVIPRIYA R</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SREEDHARANI_14</t>
+          <t>KAVI_RAVI</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE C</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+          <t>https://leetcode.com/u/KAVI_RAVI/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>922525106152</t>
+          <t>922525106332</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KAVIPRIYA R</t>
+          <t>SUBARNA V</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KAVI_RAVI</t>
+          <t>Subarna1017</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ECE C</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/KAVI_RAVI/</t>
+          <t>https://leetcode.com/u/Subarna1017/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>922525106332</t>
+          <t>922525106208</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SUBARNA V</t>
+          <t>NANDHINI D</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Subarna1017</t>
+          <t>nandhini _208</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ECE F</t>
+          <t>ECE D</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Subarna1017/</t>
+          <t>https://leetcode.com/u/nandhini _208/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>922525106208</t>
+          <t>922525106205</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NANDHINI D</t>
+          <t>MYTHILI M</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>nandhini _208</t>
+          <t>Mythili_2208</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3376,78 +3376,78 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/nandhini _208/</t>
+          <t>https://leetcode.com/u/Mythili_2208/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>922525106205</t>
+          <t>922525106079</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MYTHILI M</t>
+          <t>DHINAKAR A</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mythili_2208</t>
+          <t>dhina</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ECE D</t>
+          <t>ECE B</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/Mythili_2208/</t>
+          <t>https://leetcode.com/u/dhina/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>922525106079</t>
+          <t>922525106341</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DHINAKAR A</t>
+          <t>SURYA PRABHU S</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>dhina</t>
+          <t>SURYA_FOUNDER</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ECE B</t>
+          <t>ECE F</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/dhina/</t>
+          <t>https://leetcode.com/u/SURYA_FOUNDER/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>922525106341</t>
+          <t>922525106321</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SURYA PRABHU S</t>
+          <t>SREE DHARANI C</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SURYA_FOUNDER</t>
+          <t>SREEDHARANI_14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3457,12 +3457,1173 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://leetcode.com/u/SURYA_FOUNDER/</t>
+          <t>https://leetcode.com/u/SREEDHARANI_14/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>922525106230</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pranithaashree S</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Pranithaa_shree</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pranithaa_shree/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>922525106237</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PRIYADHARSHINI V</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>priyadharshiniveluchamy</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/priyadharshiniveluchamy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>922525106244</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RANJANA T</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>RANJANA _2007</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/RANJANA _2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>922525106250</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RESHMI R S</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Reshmi_0826</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Reshmi_0826/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>922525106320</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SOBIKA R</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>_sobika_R</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_sobika_R/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>922525106337</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SUGIDHARSHINI T</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sugi_07</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sugi_07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>922525106343</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SUTHARSHANA S</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sutharshana873</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Sutharshana873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>922525106345</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SWATHI S</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>_swathi_3366</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/_swathi_3366/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>922525106346</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>swetha E</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>swetha_20_1</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/swetha_20_1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>922525106348</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>THAMARAI SELVI D</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>thamarai_04</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thamarai_04/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>922525106351</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>THARUNIKA P</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tharunika_12</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Tharunika_12/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>922525106353</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>THIRISHA C</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>thirishavsb</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/thirishavsb/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>922525106377</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>YAZHINI V</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>YAZH_RUBA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ECE F</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/YAZH_RUBA/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>922525106219</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>NITHYASHREE P</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Nithyashree_273</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Nithyashree_273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>922525106213</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NIRANJANI D</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>niranjani _17</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/niranjani _17/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>922525106204</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MOUSHMI P N</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Moushmi_08</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Moushmi_08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>922525106203</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>MOULEESHWARI B</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MouleeshwariB</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/MouleeshwariB/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>922525106201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>MONISHA V</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MonishaV01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/MonishaV01/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>922525106191</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>MANOJ KUMAR V</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>m____a____n____o____</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/m____a____n____o____/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>922525106181</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>MADHUMITHA B</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>madhumitha-42</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/madhumitha-42/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>922525106171</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LOGASRI.A</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Loga07</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Loga07/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>922525106164</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>KOWSHIKA M S</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>kowshika_moorthi</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kowshika_moorthi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>922525106155</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>KAYALVIZHI S</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>27kayalvizhi</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/27kayalvizhi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>922525106138</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>JOTHISHA K S</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Jothi-</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Jothi-/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>922525106148</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>KAVIMALAR A</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>kavimalar08</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/kavimalar08/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>922525106136</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>JOSHITHA KS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Joshi_666</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ECE C</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Joshi_666/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>922525106119</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HAVISHMATHI S</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/e/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>922525106092</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>ELAVARASU P</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>922525106071</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DHARANI V</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/c/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>922525106065</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DHANUSHRI D</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>bo</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/bo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>922525106064</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DHANIKA S</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ECE B</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>922525106063</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DHANASRI R</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dhanasri_r</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Dhanasri_r/</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>922525106060</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>DESMA SHALINI K</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>desmashalini</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/desmashalini/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>922525106046</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BOOMIKA T</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>boomikat1206</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/boomikat1206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>922525106024</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ANUSYA B</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ANUSYA_30</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/ANUSYA_30/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>922525106023</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ANUSRI R</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Anusri_2008</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Anusri_2008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>922525106022</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>ANUJA S</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>anuja008</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/anuja008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>922525106018</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>AMIRDAVARSINI K S</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>amirda_varsini_2007</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/amirda_varsini_2007/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>922525106004</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Abirami R</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>abirami8072</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/abirami8072/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>922525106002</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>AAZHIGA N</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AAZHIGA</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/AAZHIGA/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>922525106001</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>AASHIFA SAHANAJ M</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>aashifasahanaj</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ECE A</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/aashifasahanaj/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>922525106220</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>NITHYASRI M</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>nithyam7809</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/nithyam7809/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>922525106223</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PAVITHRA S</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Pavithra145</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ECE D</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://leetcode.com/u/Pavithra145/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E112"/>
+  <autoFilter ref="A1:E155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>